--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_coquimbo.xlsx
@@ -375,76 +375,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="C2">
-        <v>212597</v>
+        <v>94.45087541600347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C3">
-        <v>181863</v>
+        <v>94.06509253350352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="C4">
-        <v>107191</v>
+        <v>93.7984496124031</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C5">
-        <v>29867</v>
+        <v>92.85872699046352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="C6">
-        <v>29480</v>
+        <v>92.43936075281901</v>
       </c>
     </row>
     <row r="7">
@@ -459,67 +459,67 @@
         </is>
       </c>
       <c r="C7">
-        <v>27203</v>
+        <v>91.93619250397107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="C8">
-        <v>25928</v>
+        <v>90.76906140974833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C9">
-        <v>21216</v>
+        <v>90.49412807445158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="C10">
-        <v>13055</v>
+        <v>89.96692392502756</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Paihuano</t>
         </is>
       </c>
       <c r="C11">
-        <v>11395</v>
+        <v>89.88656027686983</v>
       </c>
     </row>
     <row r="12">
@@ -534,67 +534,67 @@
         </is>
       </c>
       <c r="C12">
-        <v>10668</v>
+        <v>88.80379588778823</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="C13">
-        <v>8374</v>
+        <v>88.73406815413411</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paihuano</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C14">
-        <v>4675</v>
+        <v>88.7337440109514</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C15">
-        <v>4235</v>
+        <v>85.4840006755181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C16">
-        <v>4084</v>
+        <v>78.7364109846435</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C511"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -595,6 +595,7431 @@
       </c>
       <c r="C16">
         <v>78.7364109846435</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>47.81548015080949</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>47.68549280177187</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>47.56037665548894</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>47.50397916365215</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>47.23994894703254</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>46.94689625235132</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>46.82514358647096</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>46.62123793299262</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>46.26400071303366</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>46.11295681063123</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>46.10651797731205</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>46.03061948697151</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>45.90557301699956</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>45.8181228198264</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>45.40217150454243</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>45.3675185216016</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>45.10643711305233</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>45.09195656990915</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>45.04324683965402</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>44.86652977412731</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>44.86048681197524</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>44.30152232828571</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>43.86721423682409</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>43.78004229955778</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>43.43627736618663</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>43.20868475425939</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>42.65663435103458</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>42.47006744110045</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>42.22718570516911</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>41.9846997753023</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>41.18247834723238</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>40.16695393558417</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>39.75798529959692</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>39.09191583610188</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>38.8445331559104</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>37.76196885214382</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>37.47059300721993</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>36.75171120934119</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>34.83230663928816</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>34.42456110592825</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>33.83047624706617</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>33.29057732671755</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>32.32331640722551</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>32.10724573454465</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>30.68703810336094</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>28.84998892089519</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>26.40088593576966</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>26.02572632512752</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>24.76041048257145</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>24.07651492108554</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>23.72689938398357</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>23.58278531590777</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>23.2359844320984</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>23.11186825667235</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>22.83693475621034</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>22.74512180866493</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.30502098104471</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>22.16322866917319</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>21.03441645837339</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>20.55839183152521</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>20.46511627906977</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>20.41122117705819</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>20.19783024888322</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>20.1707422948922</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>20.09314703925482</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>19.69660095724832</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>19.6081757272496</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>19.05879556730741</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>19.01316741426711</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>18.76800354531354</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>18.57396318474163</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>18.56857965876357</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>18.51605758582503</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>17.85763175906913</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>17.07363968467602</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>16.8618520458747</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>16.41991065730696</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>16.17587409750953</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>16.12048233580598</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>16.01362862010221</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>15.84117206359777</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>15.69840143296495</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>15.66873038758375</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>15.66799893847156</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>15.48548447058028</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>15.36243030186503</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>15.26590483236697</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>15.07769095932737</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>15.0586864230417</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>14.96375707075839</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>14.92617130633709</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>14.89347288554686</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>14.81177275838467</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>14.80372588157019</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>14.51643914631802</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>14.44798978940651</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>14.31613099462638</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>14.21885178007061</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>14.12388774811773</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>14.09058376022324</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>14.0870155203121</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>14.0165352816766</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>13.95437455543136</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>13.89089856750109</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>13.80456459118103</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>13.77630121816168</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>13.74353320329065</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>13.72807462232586</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>13.67161533348106</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>13.67044799077101</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>13.61390961004775</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>13.58576827995861</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>13.48142888685886</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>13.38225909380983</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>13.27593691216901</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>13.19141008705077</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>13.13018506700702</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>13.11772758384668</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>13.08970099667774</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>12.98978940650925</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>12.96255262574784</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>12.86964750414005</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>12.85207363051674</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>12.82550498904843</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>12.79305589356697</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>12.78396758790334</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>12.71576695683175</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>12.63083020018291</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>12.60881190766214</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>12.48647298759677</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>12.37825688837093</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>12.34086242299795</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>12.31690622861054</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>12.26687175543165</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>12.25117442292744</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>12.18396268457173</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>12.17014900524432</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>12.16029853167843</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>12.06707734428474</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>12.06475937014859</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>11.99432221433641</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>11.99425654116146</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>11.95169867560885</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>11.94539249146758</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>11.94278110445775</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>11.89890594521245</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>11.88617391598229</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>11.87636894621562</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>11.87153931339978</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>11.86310324937512</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>11.86074124332118</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>11.82724252491694</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>11.80542203422419</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>11.79524620751197</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>11.75562328607387</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>11.70070197830249</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>11.69034146256987</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>11.6770366083056</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>11.62976783086314</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>11.60206937494699</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>11.59518773773814</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>11.54054299778766</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>11.53931339977852</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>11.52635181382615</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>11.46258220261383</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>11.42381710316886</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>11.42042247244422</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>11.39950657338876</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>11.33946414659757</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>11.22923588039867</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>11.22847634206338</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>11.21839626845717</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>11.19165750616477</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>11.17377660927826</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>11.10592825036044</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>11.08168474792597</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>10.97804391217565</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>10.95968199886428</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>10.88420059140087</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>10.79341209016558</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>10.76888987369821</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>10.76888987369821</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>10.7460643394935</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>10.57141889374386</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>10.56946598714824</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>10.47605266965707</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>10.40184579888483</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>10.30768240999123</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>10.25729834572273</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>10.14846000443164</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>10.12419605233976</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>9.947556813452094</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>9.87760686128922</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>9.8231590121352</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>9.789590254706534</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>9.414504324683966</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>9.324305017382683</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>9.10956502162553</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>8.54074752351619</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>7.939767282683094</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>7.537547028492014</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>7.466056626756588</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>5.977530981350875</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>5.29756461064255</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>5.252642970115708</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>5.201383687553307</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>4.863107460643395</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>4.668815198032398</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>4.530734721768323</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>4.378589860983934</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>4.330151428640359</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>4.269289046020381</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>4.232218036782628</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>4.058940822602994</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>3.956194387405886</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>3.768506056527591</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>3.723533706497931</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>3.486927269814744</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>3.459218883265433</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>3.288104553400483</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>3.184805067235715</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>3.137138215828033</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>3.11762643033722</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>3.076659822039699</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>3.02727877578177</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>2.946180788563364</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>2.935321904988265</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>2.904618208739398</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>2.812846068660022</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>2.680010177253838</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>2.653943899176109</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>2.588136481121497</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>2.570352315532905</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>2.499519323207076</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>2.479034709083588</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>2.458018982720857</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>2.409679272702693</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>2.358558819273622</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>2.297511029717806</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>2.193702943189596</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>2.164321984516774</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>2.112759543406835</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>2.054298788088364</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>2.045309508615188</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>2.028966859403775</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>1.98880502077856</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>1.969054837594191</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>1.967602408616742</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>1.940563317808827</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>1.89024439279769</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>1.861738535249829</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>1.818269547804968</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>1.810227665682876</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>1.752874416946433</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>1.749723145071982</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>1.731690622861054</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>1.673511293634497</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>1.661865721249723</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>1.65427726570178</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>1.649261549900301</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>1.606135146867313</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>1.564225009416522</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>1.550848212959387</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>1.462014169796299</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>1.413360782957643</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>1.396357586381057</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>1.36518771331058</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>1.340140395660498</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>1.331890452010322</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>1.307334367383115</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>1.298593190710064</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>1.268986733320515</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>1.265514723777075</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>1.248179385563798</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>1.231998668109548</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>1.195677946008197</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>1.134911910633114</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>1.130068690449812</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>1.086715457972943</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>1.063594061599823</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>1.06312292358804</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>1.049063522826882</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>1.039020424753582</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>1.023271731690623</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>1.013890297069857</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>1.005995325678285</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>0.9996666334743286</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>0.9971194327498338</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>0.9746761131975328</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>0.9738170240151746</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>0.9655664161145607</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>0.9491360428328061</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>0.937404735291129</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>0.9358566802341127</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>0.9274469541409993</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>0.9069200284523931</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>0.9036723706979427</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>0.8693070986345518</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>0.8599010302587815</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>0.8538478598358837</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>0.8481044864727334</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>0.8459911555470102</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>0.8273210717068049</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>0.8267640838300326</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>0.8205810601020181</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>0.8157829018563223</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>0.8157829018563223</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>0.8009733346851871</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>0.7717750826901875</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>0.7675345602578237</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>0.7675345602578237</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>0.7536584541552604</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>0.7524236724063088</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>0.7491883792558062</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>0.7468991855081281</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>0.736801449835111</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>0.7318695941450433</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>0.7308970099667774</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>0.7306287252451452</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>0.7306287252451452</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>0.7301046483329278</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>0.7301046483329278</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>0.7234843003906816</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>0.7131028422724661</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>0.7114016535281676</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>0.7070758391762355</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>0.7051691129546905</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>0.6962046706546352</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>0.6691675960661057</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>0.657094183499635</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>0.6565851629579013</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>0.6327573618885374</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>0.6209802616988246</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>0.6204298692665633</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>0.6204298692665633</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>0.6021541853956407</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>0.5982716596499003</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>0.5980066445182725</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>0.5966815571155073</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>0.5894326180985497</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>0.5852156057494866</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>0.5834434169969177</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>0.5768121515093251</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>0.5641380308647436</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>0.5639894835043677</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>0.5610192977119876</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>0.5575850797923476</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>0.5539552404165743</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>0.5433577289864715</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>0.5427971412119365</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>0.5385463489101857</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>0.535410075444147</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>0.53156146179402</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>0.5272978015737811</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>0.5228913514958852</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>0.5096388211832484</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>0.5094130675526024</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>0.5065023956194388</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>0.499001996007984</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>0.4919693242656634</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>0.4919693242656634</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>0.4874806115665854</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>0.4867364322219518</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>0.479908073946399</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>0.479908073946399</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>0.4658583280153159</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>0.4658583280153159</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>0.4654346338124572</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>0.4620123203285421</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>0.4596302680050018</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>0.4537359002629124</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>0.4485602662422226</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>0.4393524620636047</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>0.4211869814932993</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>0.4208194905869325</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>0.4208194905869325</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>0.4208194905869325</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>0.4138940240803197</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>0.3992015968063872</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>0.398671096345515</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>0.398671096345515</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>0.3845414343395501</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>0.3765227021040974</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>0.3689769931992476</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>0.3684007249175555</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>0.3653143626225726</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>0.3650523241664639</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>0.356940050296098</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>0.3545313538666076</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>0.35437430786268</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>0.3477983407785578</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>0.3460872909055951</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>0.3460872909055951</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>0.3416619626251522</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>0.3294041933407851</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>0.3255679351758067</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>0.3190810465858328</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>0.3183330921718999</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>0.307999667027387</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>0.3038634061640862</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>0.2999361837906828</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>0.2994011976047904</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>0.2966285631601794</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>0.2839295854628052</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>0.2807913209955329</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>0.2798744805360021</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>0.2772233311155467</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>0.2766407449999598</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>0.2595927638517077</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>0.2566735112936345</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>0.2532195051367385</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>0.2520740268028079</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>0.2459846621328317</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C430">
+        <v>0.2436323366555925</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>0.2328675981370592</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>0.2328675981370592</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>0.2328675981370592</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>0.221483942414175</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>0.2074026802807913</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>0.2025756041093908</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>0.1997835678015483</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>0.1996007984031936</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>0.1914486279514997</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>0.1735934694983572</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>0.152658807565092</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>0.1519317030820431</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C443">
+        <v>0.1487039102369124</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C444">
+        <v>0.1340140395660498</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C445">
+        <v>0.1329492576999778</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C446">
+        <v>0.1300479123887748</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C447">
+        <v>0.1272854007108933</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C448">
+        <v>0.1248647298759677</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C449">
+        <v>0.1218099171098369</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C450">
+        <v>0.1187346281061827</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C451">
+        <v>0.1182872013248167</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C452">
+        <v>0.115362430301865</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C453">
+        <v>0.1112664897370734</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C454">
+        <v>0.09253350350989151</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C455">
+        <v>0.08871146595697493</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C456">
+        <v>0.08041882122091855</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C457">
+        <v>0.08021628687720966</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C458">
+        <v>0.08021628687720966</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C459">
+        <v>0.06774379297496867</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C460">
+        <v>0.06232458644621187</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C461">
+        <v>0.05817932922655715</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C462">
+        <v>0.05787874403125452</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C463">
+        <v>0.05768121515093251</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C464">
+        <v>0.04867364322219518</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C465">
+        <v>0.04791238877481177</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C466">
+        <v>0.04664574675600034</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C467">
+        <v>0.04431641923332594</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C468">
+        <v>0.03845414343395501</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C469">
+        <v>0.03617421501953408</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C470">
+        <v>0.03556549131185855</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C471">
+        <v>0.02703707458852952</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C472">
+        <v>0.02452774047238016</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C473">
+        <v>0.02433682161109759</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C474">
+        <v>0.02217786648924373</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C475">
+        <v>0.02215820961666297</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C476">
+        <v>0.02215820961666297</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C477">
+        <v>0.02116993530467771</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C478">
+        <v>0.01782584152826881</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C479">
+        <v>0.0160189109738199</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C480">
+        <v>0.01276324186343331</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C481">
+        <v>0.01013890297069857</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C482">
+        <v>0.003190810465858328</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C511">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
